--- a/SGC-CKN/Excel/bf0c6544-08d4-4c90-9802-3661aefc985c_Thi_công_cọc_khoan_nhồi_P1_D800_07-07-2026.xlsx
+++ b/SGC-CKN/Excel/bf0c6544-08d4-4c90-9802-3661aefc985c_Thi_công_cọc_khoan_nhồi_P1_D800_07-07-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1</t>
+    <t>P1-70</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>08:05 07/07/2026</t>
+    <t>09:05 07/07/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -95,10 +95,12 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:20</t>
+    <t xml:space="preserve">08:05
+07/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:20
+07/07/2026</t>
   </si>
   <si>
     <t/>
@@ -110,7 +112,8 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t>09:37</t>
+    <t xml:space="preserve">09:37
+07/07/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -119,7 +122,8 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t>10:00</t>
+    <t xml:space="preserve">10:00
+07/07/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -128,7 +132,8 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t>10:40</t>
+    <t xml:space="preserve">10:40
+07/07/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -137,7 +142,8 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t>11:25</t>
+    <t xml:space="preserve">11:25
+07/07/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -146,7 +152,8 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t>13:00</t>
+    <t xml:space="preserve">13:00
+07/07/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -155,7 +162,8 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t>14:02</t>
+    <t xml:space="preserve">14:02
+07/07/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -164,7 +172,8 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t>15:51</t>
+    <t xml:space="preserve">15:51
+07/07/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>

--- a/SGC-CKN/Excel/bf0c6544-08d4-4c90-9802-3661aefc985c_Thi_công_cọc_khoan_nhồi_P1_D800_07-07-2026.xlsx
+++ b/SGC-CKN/Excel/bf0c6544-08d4-4c90-9802-3661aefc985c_Thi_công_cọc_khoan_nhồi_P1_D800_07-07-2026.xlsx
@@ -95,7 +95,7 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
-    <t xml:space="preserve">08:05
+    <t xml:space="preserve">09:05
 07/07/2026</t>
   </si>
   <si>
@@ -322,17 +322,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -353,6 +348,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -493,44 +493,44 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1142,19 +1142,19 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>0.7</v>
+        <v>-9</v>
       </c>
       <c r="G11" s="5">
-        <v>-3.25</v>
+        <v>-3.95</v>
       </c>
       <c r="H11" s="5">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>3.95</v>
+        <v>5.05</v>
       </c>
       <c r="J11" s="8">
-        <v>3.16</v>
+        <v>20.2</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1177,10 +1177,10 @@
         <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>-3.25</v>
+        <v>-3.95</v>
       </c>
       <c r="G12" s="9">
-        <v>-6.35</v>
+        <v>-7.05</v>
       </c>
       <c r="H12" s="9">
         <v>0.28</v>
@@ -1188,7 +1188,7 @@
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="8">
         <v>10.94</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1196,142 +1196,142 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
-        <v>-6.35</v>
-      </c>
-      <c r="G13" s="13">
-        <v>-9.6</v>
-      </c>
-      <c r="H13" s="13">
+      <c r="F13" s="12">
+        <v>-7.05</v>
+      </c>
+      <c r="G13" s="12">
+        <v>-10.3</v>
+      </c>
+      <c r="H13" s="12">
         <v>0.38</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>3.25</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="8">
         <v>8.48</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="16">
-        <v>-9.6</v>
-      </c>
-      <c r="G14" s="16">
-        <v>-11.8</v>
-      </c>
-      <c r="H14" s="16">
+      <c r="F14" s="15">
+        <v>-10.3</v>
+      </c>
+      <c r="G14" s="15">
+        <v>-19.5</v>
+      </c>
+      <c r="H14" s="15">
         <v>0.67</v>
       </c>
-      <c r="I14" s="16">
-        <v>2.2</v>
+      <c r="I14" s="15">
+        <v>9.2</v>
       </c>
       <c r="J14" s="8">
-        <v>3.3</v>
-      </c>
-      <c r="K14" s="17" t="s">
+        <v>13.8</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="19">
-        <v>-11.8</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-23.8</v>
-      </c>
-      <c r="H15" s="19">
+      <c r="F15" s="18">
+        <v>-19.5</v>
+      </c>
+      <c r="G15" s="18">
+        <v>-24.5</v>
+      </c>
+      <c r="H15" s="18">
         <v>0.75</v>
       </c>
-      <c r="I15" s="19">
-        <v>12</v>
-      </c>
-      <c r="J15" s="12">
-        <v>16</v>
-      </c>
-      <c r="K15" s="20" t="s">
+      <c r="I15" s="18">
+        <v>5</v>
+      </c>
+      <c r="J15" s="8">
+        <v>6.67</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="22">
-        <v>-23.8</v>
-      </c>
-      <c r="G16" s="22">
-        <v>-27.8</v>
-      </c>
-      <c r="H16" s="22">
+      <c r="F16" s="21">
+        <v>-24.5</v>
+      </c>
+      <c r="G16" s="21">
+        <v>-28.5</v>
+      </c>
+      <c r="H16" s="21">
         <v>1.58</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>4</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="24">
         <v>2.53</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1352,10 +1352,10 @@
         <v>47</v>
       </c>
       <c r="F17" s="25">
-        <v>-27.8</v>
+        <v>-28.5</v>
       </c>
       <c r="G17" s="25">
-        <v>-39.2</v>
+        <v>-39.9</v>
       </c>
       <c r="H17" s="25">
         <v>1.03</v>
@@ -1363,7 +1363,7 @@
       <c r="I17" s="25">
         <v>11.4</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>11.03</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1387,19 +1387,19 @@
         <v>50</v>
       </c>
       <c r="F18" s="28">
-        <v>-39.2</v>
+        <v>-39.9</v>
       </c>
       <c r="G18" s="28">
-        <v>-43.54</v>
+        <v>-44.21</v>
       </c>
       <c r="H18" s="28">
         <v>1.82</v>
       </c>
       <c r="I18" s="28">
-        <v>4.34</v>
-      </c>
-      <c r="J18" s="8">
-        <v>2.39</v>
+        <v>4.31</v>
+      </c>
+      <c r="J18" s="24">
+        <v>2.37</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>29</v>
@@ -1554,19 +1554,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0.7</v>
+        <v>-9</v>
       </c>
       <c r="F2" s="5">
-        <v>-3.25</v>
+        <v>-3.95</v>
       </c>
       <c r="G2" s="5">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>3.95</v>
+        <v>5.05</v>
       </c>
       <c r="I2" s="8">
-        <v>3.16</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1583,10 +1583,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-3.25</v>
+        <v>-3.95</v>
       </c>
       <c r="F3" s="9">
-        <v>-6.35</v>
+        <v>-7.05</v>
       </c>
       <c r="G3" s="9">
         <v>0.28</v>
@@ -1594,123 +1594,123 @@
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>10.94</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-6.35</v>
-      </c>
-      <c r="F4" s="13">
-        <v>-9.6</v>
-      </c>
-      <c r="G4" s="13">
+      <c r="E4" s="12">
+        <v>-7.05</v>
+      </c>
+      <c r="F4" s="12">
+        <v>-10.3</v>
+      </c>
+      <c r="G4" s="12">
         <v>0.38</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>3.25</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="8">
         <v>8.48</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-9.6</v>
-      </c>
-      <c r="F5" s="16">
-        <v>-11.8</v>
-      </c>
-      <c r="G5" s="16">
+      <c r="E5" s="15">
+        <v>-10.3</v>
+      </c>
+      <c r="F5" s="15">
+        <v>-19.5</v>
+      </c>
+      <c r="G5" s="15">
         <v>0.67</v>
       </c>
-      <c r="H5" s="16">
-        <v>2.2</v>
+      <c r="H5" s="15">
+        <v>9.2</v>
       </c>
       <c r="I5" s="8">
-        <v>3.3</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>-11.8</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-23.8</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="E6" s="18">
+        <v>-19.5</v>
+      </c>
+      <c r="F6" s="18">
+        <v>-24.5</v>
+      </c>
+      <c r="G6" s="18">
         <v>0.75</v>
       </c>
-      <c r="H6" s="19">
-        <v>12</v>
-      </c>
-      <c r="I6" s="12">
-        <v>16</v>
+      <c r="H6" s="18">
+        <v>5</v>
+      </c>
+      <c r="I6" s="8">
+        <v>6.67</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
-        <v>-23.8</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-27.8</v>
-      </c>
-      <c r="G7" s="22">
+      <c r="E7" s="21">
+        <v>-24.5</v>
+      </c>
+      <c r="F7" s="21">
+        <v>-28.5</v>
+      </c>
+      <c r="G7" s="21">
         <v>1.58</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="24">
         <v>2.53</v>
       </c>
     </row>
@@ -1728,10 +1728,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-27.8</v>
+        <v>-28.5</v>
       </c>
       <c r="F8" s="25">
-        <v>-39.2</v>
+        <v>-39.9</v>
       </c>
       <c r="G8" s="25">
         <v>1.03</v>
@@ -1739,7 +1739,7 @@
       <c r="H8" s="25">
         <v>11.4</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>11.03</v>
       </c>
     </row>
@@ -1757,19 +1757,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-39.2</v>
+        <v>-39.9</v>
       </c>
       <c r="F9" s="28">
-        <v>-43.54</v>
+        <v>-44.21</v>
       </c>
       <c r="G9" s="28">
         <v>1.82</v>
       </c>
       <c r="H9" s="28">
-        <v>4.34</v>
-      </c>
-      <c r="I9" s="8">
-        <v>2.39</v>
+        <v>4.31</v>
+      </c>
+      <c r="I9" s="24">
+        <v>2.37</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1786,19 +1786,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>0.7</v>
+        <v>-9</v>
       </c>
       <c r="F10" s="33">
-        <v>-43.54</v>
+        <v>-44.21</v>
       </c>
       <c r="G10" s="33">
-        <v>7.77</v>
+        <v>6.77</v>
       </c>
       <c r="H10" s="33">
-        <v>44.24</v>
+        <v>45.31</v>
       </c>
       <c r="I10" s="33">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/bf0c6544-08d4-4c90-9802-3661aefc985c_Thi_công_cọc_khoan_nhồi_P1_D800_07-07-2026.xlsx
+++ b/SGC-CKN/Excel/bf0c6544-08d4-4c90-9802-3661aefc985c_Thi_công_cọc_khoan_nhồi_P1_D800_07-07-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>09:05 07/07/2026</t>
+    <t>09:05 07/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>15:51 07/07/2026</t>
+    <t>15:51 07/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -96,11 +96,11 @@
   </si>
   <si>
     <t xml:space="preserve">09:05
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">09:20
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t/>
@@ -113,7 +113,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:37
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -123,7 +123,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:00
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -133,7 +133,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:40
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -143,7 +143,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:25
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -153,7 +153,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:00
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -163,7 +163,7 @@
   </si>
   <si>
     <t xml:space="preserve">14:02
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -173,7 +173,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:51
-07/07/2026</t>
+07/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
